--- a/artfynd/A 29672-2024 artfynd.xlsx
+++ b/artfynd/A 29672-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103400843</v>
+        <v>103400841</v>
       </c>
       <c r="B2" t="n">
-        <v>94440</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1841</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565745.6655648721</v>
+        <v>565745</v>
       </c>
       <c r="R2" t="n">
-        <v>6966566.045184438</v>
+        <v>6966566</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,19 +745,9 @@
           <t>2022-09-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,15 +774,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103400841</v>
+        <v>103401629</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,36 +785,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>388</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norr om bräntbergets nr, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565745.6655648721</v>
+        <v>565873</v>
       </c>
       <c r="R3" t="n">
-        <v>6966566.045184438</v>
+        <v>6966556</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +843,9 @@
           <t>2022-09-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,6 +869,105 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>103400843</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97453</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1841</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedflikmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lophozia guttulata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norr om bräntbergets nr, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>565745</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6966566</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-09-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-09-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29672-2024 artfynd.xlsx
+++ b/artfynd/A 29672-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103400841</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -869,6 +879,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401629</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,8 +983,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103400843</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>